--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/матрица КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/матрица КИ.xlsx
@@ -1,405 +1,766 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\поком_подтянуть_su\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F566F583-7AD4-431D-88B7-DFB486F0F0BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0ADC3A-7DC3-44E1-B649-EB609A4BABDB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+  <si>
+    <t>Номенклатура</t>
+  </si>
+  <si>
+    <t>№ п/п</t>
+  </si>
   <si>
     <t xml:space="preserve"> 005  Колбаса Докторская ГОСТ, Вязанка вектор,ВЕС. ПОКОМ</t>
   </si>
   <si>
+    <t>SU000722</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 016  Сосиски Вязанка Молочные, Вязанка вискофан  ВЕС.ПОКОМ</t>
   </si>
   <si>
+    <t>SU001523</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 017  Сосиски Вязанка Сливочные, Вязанка амицел ВЕС.ПОКОМ</t>
   </si>
   <si>
+    <t>SU001721</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 023  Колбаса Докторская ГОСТ, Вязанка вектор, 0,4 кг, ПОКОМ</t>
   </si>
   <si>
+    <t>SU001485</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 030  Сосиски Вязанка Молочные, Вязанка вискофан МГС, 0.45кг, ПОКОМ</t>
   </si>
   <si>
+    <t>SU001718</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 032  Сосиски Вязанка Сливочные, Вязанка амицел МГС, 0.45кг, ПОКОМ</t>
   </si>
   <si>
+    <t>SU001720</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 047  Кол Баварская, белков.обол. в термоусад. пакете 0.17 кг, ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002092</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 062  Колбаса Кракушка пряная с сальцем, 0.3кг в/у п/к, БАВАРУШКА ПОКОМ</t>
   </si>
   <si>
+    <t>SU002252</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 083  Колбаса Швейцарская 0,17 кг., ШТ., сырокопченая   ПОКОМ</t>
   </si>
   <si>
+    <t>SU001869</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 200  Ветчина Дугушка ТМ Стародворье, вектор в/у    ПОКОМ</t>
   </si>
   <si>
+    <t>SU002035</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 201  Ветчина Нежная ТМ Особый рецепт, (2,5кг), ПОКОМ</t>
   </si>
   <si>
+    <t>SU000126</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 215  Колбаса Докторская ГОСТ Дугушка, ВЕС, ТМ Стародворье ПОКОМ</t>
   </si>
   <si>
+    <t>SU002011</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 225  Колбаса Дугушка со шпиком, ВЕС, ТМ Стародворье   ПОКОМ</t>
   </si>
   <si>
+    <t>SU002182</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 226  Колбаса Княжеская, с/к белков.обол в термоусад. пакете, ВЕС, ТМ Стародворье ПОКОМ</t>
   </si>
   <si>
+    <t>SU001920</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 229  Колбаса Молочная Дугушка, в/у, ВЕС, ТМ Стародворье   ПОКОМ</t>
   </si>
   <si>
+    <t>SU002010</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 236  Колбаса Рубленая ЗАПЕЧ. Дугушка ТМ Стародворье, вектор, в/к    ПОКОМ</t>
   </si>
   <si>
+    <t>SU002150</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 239  Колбаса Салями запеч Дугушка, оболочка вектор, ВЕС, ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002158</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 240  Колбаса Салями охотничья, ВЕС. ПОКОМ</t>
   </si>
   <si>
+    <t>SU001921</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 242  Колбаса Сервелат ЗАПЕЧ.Дугушка ТМ Стародворье, вектор, в/к     ПОКОМ</t>
   </si>
   <si>
+    <t>SU002151</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 244  Колбаса Сервелат Кремлевский, ВЕС. ПОКОМ</t>
   </si>
   <si>
+    <t>SU001822</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 247  Сардельки Нежные, ВЕС.  ПОКОМ</t>
   </si>
   <si>
+    <t>SU001051</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 248  Сардельки Сочные ТМ Особый рецепт,   ПОКОМ</t>
   </si>
   <si>
+    <t>SU002287</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250  Сардельки стародворские с говядиной в обол. NDX, ВЕС. ПОКОМ</t>
   </si>
   <si>
+    <t>SU000227</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 255  Сосиски Молочные для завтрака ТМ Особый рецепт, п/а МГС, ВЕС, ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002074</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 257  Сосиски Молочные оригинальные ТМ Особый рецепт, ВЕС.   ПОКОМ</t>
   </si>
   <si>
+    <t>SU000246</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 263  Шпикачки Стародворские, ВЕС.  ПОКОМ</t>
   </si>
   <si>
+    <t>SU001430</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 265  Колбаса Балыкбургская, ВЕС, ТМ Баварушка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002612</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 267  Колбаса Салями Филейбургская зернистая, оболочка фиброуз, ВЕС, ТМ Баварушка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002614</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 273  Сосиски Сочинки с сочной грудинкой, МГС 0.4кг,   ПОКОМ</t>
   </si>
   <si>
+    <t>SU002618</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 276  Колбаса Сливушка ТМ Вязанка в оболочке полиамид 0,45 кг  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002734</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 278  Сосиски Сочинки с сочным окороком, МГС 0.4кг,   ПОКОМ</t>
   </si>
   <si>
+    <t>SU002621</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 281  Сосиски Молочные для завтрака ТМ Особый рецепт, 0,4кг  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002205</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 283  Сосиски Сочинки, ВЕС, ТМ Стародворье ПОКОМ</t>
   </si>
   <si>
+    <t>SU002725</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 285  Паштет печеночный со слив.маслом ТМ Стародворье ламистер 0,1 кг  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002368</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 296  Колбаса Мясорубская с рубленой грудинкой 0,35кг срез ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002660</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 297  Колбаса Мясорубская с рубленой грудинкой ВЕС ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002756</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 301  Сосиски Сочинки по-баварски с сыром,  0.4кг, ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002801</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 302  Сосиски Сочинки по-баварски,  0.4кг, ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002799</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 305  Колбаса Сервелат Мясорубский с мелкорубленным окороком в/у  ТМ Стародворье ВЕС   ПОКОМ</t>
   </si>
   <si>
+    <t>SU002847</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 307  Колбаса Сервелат Мясорубский с мелкорубленным окороком 0,35 кг срез ТМ Стародворье   Поком</t>
   </si>
   <si>
+    <t>SU002848</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 309  Сосиски Сочинки с сыром 0,4 кг ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002686</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 312  Ветчина Филейская ВЕС ТМ  Вязанка ТС Столичная  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002828</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 315  Колбаса вареная Молокуша ТМ Вязанка ВЕС, ПОКОМ</t>
   </si>
   <si>
+    <t>SU002830</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 318  Сосиски Датские ТМ Зареченские, ВЕС  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004392</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 319  Колбаса вареная Филейская ТМ Вязанка ТС Классическая, 0,45 кг. ПОКОМ</t>
   </si>
   <si>
+    <t>SU002815</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 322  Колбаса вареная Молокуша 0,45кг ТМ Вязанка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002816</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 328  Сардельки Сочинки Стародворье ТМ  0,4 кг ПОКОМ</t>
   </si>
   <si>
+    <t>SU002758</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 329  Сардельки Сочинки с сыром Стародворье ТМ, 0,4 кг. ПОКОМ</t>
   </si>
   <si>
+    <t>SU002759</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 330  Колбаса вареная Филейская ТМ Вязанка ТС Классическая ВЕС  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002829</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 334  Паштет Любительский ТМ Стародворье ламистер 0,1 кг  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002841</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 335  Колбаса Сливушка ТМ Вязанка. ВЕС.  ПОКОМ </t>
   </si>
   <si>
+    <t>SU002928</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 336  Ветчина Сливушка с индейкой ТМ Вязанка. ВЕС  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002833</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 338  Паштет печеночный с морковью ТМ Стародворье ламистер 0,1 кг.  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002840</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 339  Колбаса вареная Филейская ТМ Вязанка ТС Классическая, 0,40 кг.  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002831</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 340  Сосиски Сочинки Молочные ТМ Стародворье, ВЕС ПОКОМ</t>
   </si>
   <si>
+    <t>SU002843</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 341 Сосиски Сочинки Сливочные ТМ Стародворье ВЕС ПОКОМ</t>
   </si>
   <si>
+    <t>SU002845</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 342 Сосиски Сочинки Молочные ТМ Стародворье 0,4 кг ПОКОМ</t>
   </si>
   <si>
+    <t>SU002842</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 343 Сосиски Сочинки Сливочные ТМ Стародворье  0,4 кг ПОКОМ</t>
   </si>
   <si>
+    <t>SU002844</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 344  Колбаса Сочинка по-европейски с сочной грудинкой ТМ Стародворье, ВЕС ПОКОМ</t>
   </si>
   <si>
+    <t>SU002941</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 345  Колбаса Сочинка по-фински с сочным окроком ТМ Стародворье ВЕС ПОКОМ</t>
   </si>
   <si>
+    <t>SU002943</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 346  Колбаса Сочинка зернистая с сочной грудинкой ТМ Стародворье.ВЕС ПОКОМ</t>
   </si>
   <si>
+    <t>SU002945</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 347  Колбаса Сочинка рубленая с сочным окороком ТМ Стародворье ВЕС ПОКОМ</t>
   </si>
   <si>
+    <t>SU002947</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 355  Колбаса Сервелат запеченный ТМ Стародворье ТС Дугушка. 0,6 кг. ПОКОМ</t>
   </si>
   <si>
+    <t>SU002918</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 364  Сардельки Филейские Вязанка ВЕС NDX ТМ Вязанка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002835</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 376  Колбаса Докторская Дугушка 0,6кг ГОСТ ТМ Стародворье  ПОКОМ </t>
   </si>
   <si>
+    <t>SU002632</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 377  Колбаса Молочная Дугушка 0,6кг ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002631</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 387  Колбаса вареная Мусульманская Халяль ТМ Вязанка, 0,4 кг ПОКОМ</t>
   </si>
   <si>
+    <t>SU002983</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 388  Сосиски Восточные Халяль ТМ Вязанка 0,33 кг АК. ПОКОМ</t>
   </si>
   <si>
+    <t>SU002984</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 394 Колбаса полукопченая Аль-Ислами халяль ТМ Вязанка оболочка фиброуз в в/у 0,35 кг  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002985</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 395  Колбаса Докторская ГОСТ ТМ Вязанка в оболочке полиамид 0,37 кг. ПОКОМ</t>
   </si>
   <si>
+    <t>SU002986</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 397  Ветчина Дугушка ТМ Стародворье ТС Дугушка в полиамидной оболочке 0,6 кг. ПОКОМ</t>
   </si>
   <si>
+    <t>SU002643</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 405  Сардельки Сливушки ТМ Вязанка в оболочке айпил 0,33 кг. ПОКОМ</t>
   </si>
   <si>
+    <t>SU002367</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 408  Ветчина Сливушка с индейкой ТМ Вязанка, 0,4кг  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002735</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 410  Сосиски Баварские с сыром ТМ Стародворье 0,35 кг. ПОКОМ</t>
   </si>
   <si>
+    <t>SU003168</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 412  Сосиски Баварские ТМ Стародворье 0,35 кг ПОКОМ</t>
   </si>
   <si>
+    <t>SU003167</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 430  Колбаса Стародворская с окороком 0,4 кг. ТМ Стародворье в оболочке полиамид  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003272</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 433 Колбаса Стародворская со шпиком  в оболочке полиамид. ТМ Стародворье ВЕС ПОКОМ</t>
   </si>
   <si>
+    <t>SU003275</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 436  Колбаса Молочная стародворская с молоком, ВЕС, ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003273</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 449  Колбаса Дугушка Стародворская ВЕС ТС Дугушка ПОКОМ</t>
   </si>
   <si>
+    <t>SU002634</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 451 Сосиски Филейские ТМ Вязанка в оболочке целлофан 0,3 кг. ПОКОМ</t>
   </si>
   <si>
+    <t>SU002825</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 452  Колбаса Со шпиком ВЕС большой батон ТМ Особый рецепт  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003423</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 456  Колбаса Филейная ТМ Особый рецепт ВЕС большой батон  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003420</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 457  Колбаса Молочная ТМ Особый рецепт ВЕС большой батон  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003422</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 460  Колбаса Стародворская Традиционная ВЕС ТМ Стародворье в оболочке полиамид. ПОКОМ</t>
   </si>
   <si>
+    <t>SU003392</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 498  Колбаса Сочинка рубленая с сочным окороком 0,3кг ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002948</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 517  Сосиски С сыром ТМ Ядрена копоть 0,3кг  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003665</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 523  Колбаса Сальчичон нарезка 0,07кг ТМ Стародворье  ПОКОМ </t>
   </si>
   <si>
+    <t>SU003893</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 524  Колбаса Сервелат Ореховый нарезка 0,07кг ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003894</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 525  Колбаса Фуэт нарезка 0,07кг ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003896</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 544  Сосиски Мясные для гриля ТС Ядрена копоть 0,3 кг  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004016</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 547  Колбаса Мясная Классическая ТМ Вязанка в оболочке полиамид. ВЕС  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004157</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 551  Колбаса Сливушка ТМ Вязанка в модифицированной газовой среде 0,11 кг нарезка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003745</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 552  Ветчина Сливушка с индейкой ТМ Вязанка в модифицированной газовой среде 0,1 кг нарезка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002356</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 553  Ассорти колбас Мясорубская коллекция: Сервелат Делюкс, С балыком 0,08 кг нарезка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004026</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 554  Колбаса Сервелат Мясорубский ТМ Стародворье в упаковке скин 0,08 кг нарезка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003178</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 555  Колбаса Молокуша ТМ Вязанка в модифицированной газовой среде 0,17 кг нарезка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002354</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 556  Колбаса Сервелат Ореховый ТМ Вязанка в оболочке фиброуз в вакуумной упаковке, ВЕС  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004044</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 557  Колбаса Сервелат Финский ТМ Вязанка в оболочке фиброуз в вакуумной упаковке, ВЕС  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004047</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 558  Колбаса Балыковая НОВАЯ ВЕС Вязанка фиброуз в/у ПОКОМ</t>
   </si>
   <si>
+    <t>SU004041</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 564  Сосиски Сочные 0,3 кг ТМ Вязанка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004053</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 567 Колбаса Со шпиком Стародворская ТМ Стародворье в оболочке полиамид ВЕС  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004007</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 569  Колбаса Балыковая ТМ Вязанка в оболочке фиброуз в вакуумной упаковке 0,28 кг срез.  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004039</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 570  Колбаса Сервелат Финский ТМ Вязанка в оболочке фиброуз в вак. упаковке 0,28 кг срез  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004045</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 571  Колбаса Сервелат Ореховый ТМ Вязанка в оболочке фиброуз в вак. упаковке 0,28 кг срез  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004042</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 574  Колбаса Сервелат Финский ТМ Вязанка в упаковке скин 0,09 кг нарезка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003751</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 579  Колбаса Ветчинно-рубленая ТМ Особый рецепт в оболочке полиамид.ВЕС  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004131</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 580  Ветчина Нежная с индейкой ТМ Особый рецепт в оболочке полиамид.ВЕС  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003686</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 583  Колбаса Балыковая ТМ Вязанка в упаковке скин 0,09 кг нарезка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003753</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 584  Колбаса Сервелат Ореховый ТМ Вязанка в упаковке скин 0,09 кг нарезка  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003988</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 585  Колбаса Молочная ТМ Стародворье в оболочке вектор НД ВЕС.  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004103</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 586  Колбаса Мясная ТМ Стародворье в оболочке вектор НД ВЕС.  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004104</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 588 Колбаса Со шпиком ТМ Стародворье в оболочке вектор ВЕС  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004106</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 597  Колбаса Классическая ТМ Особый рецепт в оболочке полиамид ВЕС. ПОКОМ</t>
   </si>
   <si>
+    <t>SU004238</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 614  Буженина в пряном маринаде 0,25 кг консервы из мяса индейки ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004146</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 615  Гречка по-купечески с говядиной и овощами 0,325кг ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004144</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 616  Индейка томлёная в собственном соку 0,25кг ТМ Стародлворье Консервый из мяс.птицы  ПОКОМ</t>
   </si>
   <si>
+    <t>SU004145</t>
+  </si>
+  <si>
     <t>495  Колбаса Сочинка по-европейски с сочной грудинкой 0,3кг ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002944</t>
+  </si>
+  <si>
     <t>496  Колбаса Сочинка по-фински с сочным окроком 0,3кг ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU002942</t>
+  </si>
+  <si>
     <t>503 Колбаса Филейская со шпиком ТМ Вязанка в оболочке полиамид.ПОКОМ</t>
   </si>
   <si>
+    <t>SU003642</t>
+  </si>
+  <si>
     <t>515  Колбаса Сервелат Мясорубский Делюкс 0,3кг ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
+    <t>SU003829</t>
+  </si>
+  <si>
     <t>519  Грудинка 0,12 кг нарезка ТМ Стародворье  ПОКОМ</t>
   </si>
   <si>
-    <t>№ п/п</t>
-  </si>
-  <si>
-    <t>Номенклатура</t>
+    <t>SU003921</t>
+  </si>
+  <si>
+    <t>нет в бланке</t>
+  </si>
+  <si>
+    <t>комментарий</t>
+  </si>
+  <si>
+    <t>SU</t>
   </si>
 </sst>
 </file>
@@ -415,12 +776,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -450,12 +817,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -736,987 +1107,1481 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B122"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="101" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="3" max="3" width="101" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="1"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="1"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="1"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="1"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" s="1"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" s="1"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D52" s="1"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" s="1"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D54" s="1"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D55" s="1"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D56" s="1"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" s="1"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D58" s="1"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="1"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D60" s="1"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D61" s="1"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D62" s="1"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D63" s="1"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D64" s="1"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D65" s="1"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D66" s="1"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D67" s="1"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D68" s="1"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D69" s="1"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D70" s="1"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D71" s="1"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D72" s="1"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D73" s="1"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D74" s="1"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D75" s="1"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D76" s="1"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D77" s="1"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D78" s="1"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D79" s="1"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D80" s="1"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D81" s="1"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D82" s="1"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D83" s="1"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D84" s="1"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D85" s="1"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D86" s="1"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D87" s="1"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D88" s="1"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B89" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D89" s="1"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D90" s="1"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B91" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D91" s="1"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D92" s="1"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+      <c r="B93" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D93" s="1"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
         <v>93</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>94</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D95" s="1"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>95</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D96" s="1"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" s="1"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D98" s="1"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>98</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D99" s="1"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>99</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D100" s="1"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>100</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D101" s="1"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>101</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D102" s="1"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>102</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D103" s="1"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>103</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D104" s="1"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>104</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D105" s="1"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>105</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D106" s="1"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>106</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D107" s="1"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>107</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D108" s="1"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>108</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D109" s="1"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>109</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D110" s="1"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>110</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D111" s="1"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>111</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D112" s="1"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>112</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D113" s="1"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>113</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D114" s="1"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>114</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D115" s="1"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>115</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D116" s="1"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>116</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D117" s="1"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>117</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D118" s="1"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>118</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D119" s="1"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>119</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D120" s="1"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>120</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D121" s="1"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>121</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>120</v>
-      </c>
+      <c r="B122" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D122" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
